--- a/LISTAS/ma/SOP. CAÑOS CURVOS.xlsx
+++ b/LISTAS/ma/SOP. CAÑOS CURVOS.xlsx
@@ -831,14 +831,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="22" t="n">
-        <v>45195.54867970475</v>
+        <v>45253</v>
       </c>
       <c r="E1" s="5" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="19">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -860,8 +856,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10"/>
     <row r="11" ht="41.25" customHeight="1" s="19">
       <c r="A11" s="20" t="inlineStr">
         <is>
@@ -891,7 +885,6 @@
     <row r="25" ht="17.25" customHeight="1" s="19"/>
     <row r="26" ht="17.25" customHeight="1" s="19"/>
     <row r="27" ht="17.25" customHeight="1" s="19"/>
-    <row r="28"/>
     <row r="29" ht="18" customHeight="1" s="19">
       <c r="A29" s="8" t="inlineStr">
         <is>
@@ -963,12 +956,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="A12:D12"/>
     <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="A1:D1"/>
     <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/SOP. CAÑOS CURVOS.xlsx
+++ b/LISTAS/ma/SOP. CAÑOS CURVOS.xlsx
@@ -831,7 +831,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="22" t="n">
-        <v>45253</v>
+        <v>45254</v>
       </c>
       <c r="E1" s="5" t="n"/>
     </row>

--- a/LISTAS/ma/SOP. CAÑOS CURVOS.xlsx
+++ b/LISTAS/ma/SOP. CAÑOS CURVOS.xlsx
@@ -831,7 +831,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="22" t="n">
-        <v>45254</v>
+        <v>45255</v>
       </c>
       <c r="E1" s="5" t="n"/>
     </row>

--- a/LISTAS/ma/SOP. CAÑOS CURVOS.xlsx
+++ b/LISTAS/ma/SOP. CAÑOS CURVOS.xlsx
@@ -831,7 +831,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="22" t="n">
-        <v>45255</v>
+        <v>45256</v>
       </c>
       <c r="E1" s="5" t="n"/>
     </row>

--- a/LISTAS/ma/SOP. CAÑOS CURVOS.xlsx
+++ b/LISTAS/ma/SOP. CAÑOS CURVOS.xlsx
@@ -831,7 +831,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="22" t="n">
-        <v>45256</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="5" t="n"/>
     </row>

--- a/LISTAS/ma/SOP. CAÑOS CURVOS.xlsx
+++ b/LISTAS/ma/SOP. CAÑOS CURVOS.xlsx
@@ -831,10 +831,14 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="22" t="n">
-        <v>45266</v>
+        <v>45265.55811163934</v>
       </c>
       <c r="E1" s="5" t="n"/>
     </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="19">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -856,6 +860,8 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
+    <row r="10"/>
     <row r="11" ht="41.25" customHeight="1" s="19">
       <c r="A11" s="20" t="inlineStr">
         <is>
@@ -885,6 +891,7 @@
     <row r="25" ht="17.25" customHeight="1" s="19"/>
     <row r="26" ht="17.25" customHeight="1" s="19"/>
     <row r="27" ht="17.25" customHeight="1" s="19"/>
+    <row r="28"/>
     <row r="29" ht="18" customHeight="1" s="19">
       <c r="A29" s="8" t="inlineStr">
         <is>
@@ -917,7 +924,7 @@
       </c>
       <c r="C30" s="17" t="n"/>
       <c r="D30" s="6" t="n">
-        <v>936</v>
+        <v>1430</v>
       </c>
       <c r="E30" s="2" t="n"/>
     </row>
@@ -934,7 +941,7 @@
       </c>
       <c r="C31" s="17" t="n"/>
       <c r="D31" s="7" t="n">
-        <v>1040</v>
+        <v>1590</v>
       </c>
       <c r="E31" s="2" t="n"/>
     </row>
@@ -956,12 +963,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B29:C29"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A12:D12"/>
     <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="A11:D11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>
